--- a/Tabela_Q5_metricas.xlsx
+++ b/Tabela_Q5_metricas.xlsx
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>4</v>
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>6</v>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="8">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
